--- a/BWI/bestwine_output/bestwine_Malaysia.xlsx
+++ b/BWI/bestwine_output/bestwine_Malaysia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA148"/>
+  <dimension ref="A1:AA150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15410,6 +15410,232 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>9541</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Jalan 1/89B</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>57100</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>https://eluenheng.luenheng.com, https://luenheng.com</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>sean@luenheng.com</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7983 9000</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>200801034172</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/luen-heng-f-&amp;-b-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LuenHengMalaysia/</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luenheng/</t>
+        </is>
+      </c>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr"/>
+      <c r="W149" s="2" t="inlineStr">
+        <is>
+          <t>Loo Eric</t>
+        </is>
+      </c>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/loo-eric-a03a91129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>9541</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Jalan 1/89B</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>57100</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://eluenheng.luenheng.com, https://luenheng.com</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>sean@luenheng.com</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7983 9000</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>200801034172</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/luen-heng-f-&amp;-b-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LuenHengMalaysia/</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luenheng/</t>
+        </is>
+      </c>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr"/>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>Sean Soh</t>
+        </is>
+      </c>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/sean-soh-06572593/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Malaysia.xlsx
+++ b/BWI/bestwine_output/bestwine_Malaysia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA150"/>
+  <dimension ref="A1:AA152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15636,6 +15636,232 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>9541</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Jalan 1/89B</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>57100</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://eluenheng.luenheng.com, https://luenheng.com</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>sean@luenheng.com</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7983 9000</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>200801034172</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/luen-heng-f-&amp;-b-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LuenHengMalaysia/</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luenheng/</t>
+        </is>
+      </c>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr"/>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
+          <t>Loo Eric</t>
+        </is>
+      </c>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/loo-eric-a03a91129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>9541</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Jalan 1/89B</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>57100</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://eluenheng.luenheng.com, https://luenheng.com</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>sean@luenheng.com</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7983 9000</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>200801034172</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/luen-heng-f-&amp;-b-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LuenHengMalaysia/</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luenheng/</t>
+        </is>
+      </c>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr"/>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>Sean Soh</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/sean-soh-06572593/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Malaysia.xlsx
+++ b/BWI/bestwine_output/bestwine_Malaysia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA152"/>
+  <dimension ref="A1:AA155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15862,6 +15862,337 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Actas Trading Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Actas Trading Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>55025</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>42 Persiaran Industri</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>52200</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.actas.com.my</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>actas1933@gmail.com</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-6262 7799</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>434719V</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr"/>
+      <c r="S153" s="2" t="inlineStr"/>
+      <c r="T153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC-x0nnaSbmTlGkCG_EuieRA</t>
+        </is>
+      </c>
+      <c r="W153" s="2" t="inlineStr">
+        <is>
+          <t>Conners Francis</t>
+        </is>
+      </c>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brand &amp; Marketing Manager </t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/conners-francis-1464a132/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>9541</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Jalan 1/89B</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>57100</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://eluenheng.luenheng.com, https://luenheng.com</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>sean@luenheng.com</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7983 9000</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>200801034172</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/luen-heng-f-&amp;-b-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LuenHengMalaysia/</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luenheng/</t>
+        </is>
+      </c>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>Loo Eric</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/loo-eric-a03a91129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>9541</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Jalan 1/89B</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>57100</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>https://eluenheng.luenheng.com, https://luenheng.com</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>sean@luenheng.com</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7983 9000</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>200801034172</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/luen-heng-f-&amp;-b-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LuenHengMalaysia/</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luenheng/</t>
+        </is>
+      </c>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>Sean Soh</t>
+        </is>
+      </c>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/sean-soh-06572593/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Malaysia.xlsx
+++ b/BWI/bestwine_output/bestwine_Malaysia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA155"/>
+  <dimension ref="A1:AA158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16193,6 +16193,337 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Actas Trading Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Actas Trading Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>55025</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>42 Persiaran Industri</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>52200</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.actas.com.my</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>actas1933@gmail.com</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-6262 7799</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>434719V</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr"/>
+      <c r="S156" s="2" t="inlineStr"/>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC-x0nnaSbmTlGkCG_EuieRA</t>
+        </is>
+      </c>
+      <c r="W156" s="2" t="inlineStr">
+        <is>
+          <t>Conners Francis</t>
+        </is>
+      </c>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brand &amp; Marketing Manager </t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/conners-francis-1464a132/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>9541</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Jalan 1/89B</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>57100</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>https://eluenheng.luenheng.com, https://luenheng.com</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>sean@luenheng.com</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7983 9000</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>200801034172</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/luen-heng-f-&amp;-b-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LuenHengMalaysia/</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luenheng/</t>
+        </is>
+      </c>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr">
+        <is>
+          <t>Sean Soh</t>
+        </is>
+      </c>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/sean-soh-06572593/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Luen Heng F &amp; B Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>9541</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Jalan 1/89B</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>57100</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://eluenheng.luenheng.com, https://luenheng.com</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>sean@luenheng.com</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7983 9000</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>200801034172</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/luen-heng-f-&amp;-b-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LuenHengMalaysia/</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luenheng/</t>
+        </is>
+      </c>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr">
+        <is>
+          <t>Loo Eric</t>
+        </is>
+      </c>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/loo-eric-a03a91129/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Malaysia.xlsx
+++ b/BWI/bestwine_output/bestwine_Malaysia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA158"/>
+  <dimension ref="A1:AA163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16524,6 +16524,571 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Gch Retail (malaysia) Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Gch Retail (malaysia) Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>108577</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Shah Alam</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Jalan Persiaran Sukan</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>40100</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.giant.com.my</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>customersupport@dfiretailgroup.com</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7723 9393</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>200401028527</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gch-retail-m-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/giantmalaysia</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/giantmalaysia/</t>
+        </is>
+      </c>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC-s4ab7Oe0UACpwhhKaz5zA</t>
+        </is>
+      </c>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
+          <t>Noor Bahrina Mohd Nor</t>
+        </is>
+      </c>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>Category Manager</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/noor-bahrina-mohd-nor-a77506214/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Gch Retail (malaysia) Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Gch Retail (malaysia) Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>108577</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Shah Alam</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Jalan Persiaran Sukan</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>40100</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.giant.com.my</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>customersupport@dfiretailgroup.com</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7723 9393</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>200401028527</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gch-retail-m-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/giantmalaysia</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/giantmalaysia/</t>
+        </is>
+      </c>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC-s4ab7Oe0UACpwhhKaz5zA</t>
+        </is>
+      </c>
+      <c r="W160" s="2" t="inlineStr">
+        <is>
+          <t>Nadzry Nordin</t>
+        </is>
+      </c>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nadzry-nordin-8857ab188/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Gch Retail (malaysia) Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Gch Retail (malaysia) Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>108577</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Shah Alam</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Jalan Persiaran Sukan</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>40100</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.giant.com.my</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>customersupport@dfiretailgroup.com</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7723 9393</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>200401028527</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gch-retail-m-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/giantmalaysia</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/giantmalaysia/</t>
+        </is>
+      </c>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC-s4ab7Oe0UACpwhhKaz5zA</t>
+        </is>
+      </c>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>Izri Shahril Bin Ishak</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/izri-shahril-bin-ishak-1a3642136/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Gch Retail (malaysia) Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Gch Retail (malaysia) Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>108577</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Shah Alam</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Jalan Persiaran Sukan</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>40100</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.giant.com.my</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>customersupport@dfiretailgroup.com</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7723 9393</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>200401028527</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gch-retail-m-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/giantmalaysia</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/giantmalaysia/</t>
+        </is>
+      </c>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC-s4ab7Oe0UACpwhhKaz5zA</t>
+        </is>
+      </c>
+      <c r="W162" s="2" t="inlineStr">
+        <is>
+          <t>Chandrasegar Muthiah</t>
+        </is>
+      </c>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Operations</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chandrasegar-muthiah-a24a53121/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Gch Retail (malaysia) Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Gch Retail (malaysia) Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>108577</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Shah Alam</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Jalan Persiaran Sukan</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>40100</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.giant.com.my</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>customersupport@dfiretailgroup.com</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7723 9393</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>200401028527</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gch-retail-m-sdn-bhd/</t>
+        </is>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/giantmalaysia</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/giantmalaysia/</t>
+        </is>
+      </c>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC-s4ab7Oe0UACpwhhKaz5zA</t>
+        </is>
+      </c>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
+          <t>Junie Chung</t>
+        </is>
+      </c>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>Senior Category Manager</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/junie-chung-685205aa/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Malaysia.xlsx
+++ b/BWI/bestwine_output/bestwine_Malaysia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA163"/>
+  <dimension ref="A1:AA164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17089,6 +17089,83 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Monopole Fine Wines Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr"/>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>168074</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Jalan PJU 3/38a</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>47810</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.monopole.com.my</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>edwin@monopole.com.my</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7733 8181</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr"/>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/monopole-fine-wines-sdn-bhd</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/drinkbetterwithus</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/monopolesg</t>
+        </is>
+      </c>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr"/>
+      <c r="X164" s="2" t="inlineStr"/>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Malaysia.xlsx
+++ b/BWI/bestwine_output/bestwine_Malaysia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA164"/>
+  <dimension ref="A1:AA165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17166,6 +17166,83 @@
       <c r="Z164" s="2" t="inlineStr"/>
       <c r="AA164" s="2" t="inlineStr"/>
     </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>My Taste Wine</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>My Taste Wine</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>122267</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Cheras</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>12a Jalan Damai Perdana 6/1C</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>43200</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>https://mytastewines.com</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>mytastewine@gmail.com</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr"/>
+      <c r="P165" s="2" t="inlineStr"/>
+      <c r="Q165" s="2" t="inlineStr"/>
+      <c r="R165" s="2" t="inlineStr"/>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mytastewine</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/mytastewine</t>
+        </is>
+      </c>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr"/>
+      <c r="X165" s="2" t="inlineStr"/>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
